--- a/salidas/empresas/KMI.xlsx
+++ b/salidas/empresas/KMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15068054199219</v>
+        <v>14.15068244934082</v>
       </c>
       <c r="C3" t="n">
         <v>29.63999938964844</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B4" t="n">
-        <v>13.71113395690918</v>
+        <v>13.7111349105835</v>
       </c>
       <c r="C4" t="n">
         <v>28.57999992370605</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B5" t="n">
-        <v>14.05175399780273</v>
+        <v>14.05175304412842</v>
       </c>
       <c r="C5" t="n">
         <v>29.29000091552734</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B6" t="n">
-        <v>13.78309917449951</v>
+        <v>13.78309345245361</v>
       </c>
       <c r="C6" t="n">
         <v>28.72999954223633</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B7" t="n">
-        <v>13.6889533996582</v>
+        <v>13.6889476776123</v>
       </c>
       <c r="C7" t="n">
         <v>28.22999954223633</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B8" t="n">
-        <v>12.53487491607666</v>
+        <v>12.53487110137939</v>
       </c>
       <c r="C8" t="n">
         <v>25.85000038146973</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B9" t="n">
-        <v>12.55426979064941</v>
+        <v>12.55427169799805</v>
       </c>
       <c r="C9" t="n">
         <v>25.88999938964844</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B10" t="n">
-        <v>14.01007652282715</v>
+        <v>14.01007461547852</v>
       </c>
       <c r="C10" t="n">
         <v>28.60000038146973</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B11" t="n">
-        <v>14.45095062255859</v>
+        <v>14.45095348358154</v>
       </c>
       <c r="C11" t="n">
         <v>29.5</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B12" t="n">
-        <v>15.75888729095459</v>
+        <v>15.75888919830322</v>
       </c>
       <c r="C12" t="n">
         <v>32.16999816894531</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B13" t="n">
-        <v>16.05741500854492</v>
+        <v>16.05742073059082</v>
       </c>
       <c r="C13" t="n">
         <v>32.47000122070312</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B14" t="n">
-        <v>17.42727851867676</v>
+        <v>17.42727470397949</v>
       </c>
       <c r="C14" t="n">
         <v>35.2400016784668</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B15" t="n">
-        <v>19.11362075805664</v>
+        <v>19.11362838745117</v>
       </c>
       <c r="C15" t="n">
         <v>38.65000152587891</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B16" t="n">
-        <v>17.91324806213379</v>
+        <v>17.91324424743652</v>
       </c>
       <c r="C16" t="n">
         <v>35.90000152587891</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B17" t="n">
-        <v>17.06000137329102</v>
+        <v>17.05999755859375</v>
       </c>
       <c r="C17" t="n">
         <v>34.18999862670898</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B18" t="n">
-        <v>16.07701683044434</v>
+        <v>16.07701110839844</v>
       </c>
       <c r="C18" t="n">
         <v>32.22000122070312</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B19" t="n">
-        <v>18.04515266418457</v>
+        <v>18.0451545715332</v>
       </c>
       <c r="C19" t="n">
         <v>35.81000137329102</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B20" t="n">
-        <v>18.02499961853027</v>
+        <v>18.02499771118164</v>
       </c>
       <c r="C20" t="n">
         <v>35.77000045776367</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B21" t="n">
-        <v>17.89901733398438</v>
+        <v>17.89902305603027</v>
       </c>
       <c r="C21" t="n">
         <v>35.52000045776367</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B22" t="n">
-        <v>17.6742057800293</v>
+        <v>17.67421340942383</v>
       </c>
       <c r="C22" t="n">
         <v>34.70999908447266</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B24" t="n">
-        <v>17.98991584777832</v>
+        <v>17.98991775512695</v>
       </c>
       <c r="C24" t="n">
         <v>35.33000183105469</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B25" t="n">
-        <v>19.26441955566406</v>
+        <v>19.2644214630127</v>
       </c>
       <c r="C25" t="n">
         <v>37.45999908447266</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B26" t="n">
-        <v>19.06386566162109</v>
+        <v>19.06386375427246</v>
       </c>
       <c r="C26" t="n">
         <v>37.06999969482422</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B27" t="n">
-        <v>19.89183235168457</v>
+        <v>19.8918285369873</v>
       </c>
       <c r="C27" t="n">
         <v>38.68000030517578</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B28" t="n">
-        <v>20.30077362060547</v>
+        <v>20.3007698059082</v>
       </c>
       <c r="C28" t="n">
         <v>39.09999847412109</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B30" t="n">
-        <v>19.80753326416016</v>
+        <v>19.80753707885742</v>
       </c>
       <c r="C30" t="n">
         <v>38.15000152587891</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B31" t="n">
-        <v>19.80974769592285</v>
+        <v>19.80974388122559</v>
       </c>
       <c r="C31" t="n">
         <v>37.7599983215332</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B32" t="n">
-        <v>19.89892768859863</v>
+        <v>19.89893531799316</v>
       </c>
       <c r="C32" t="n">
         <v>37.93000030517578</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B33" t="n">
-        <v>18.66082763671875</v>
+        <v>18.66082000732422</v>
       </c>
       <c r="C33" t="n">
         <v>35.56999969482422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B34" t="n">
-        <v>18.73722648620605</v>
+        <v>18.73722839355469</v>
       </c>
       <c r="C34" t="n">
         <v>35.31000137329102</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B36" t="n">
-        <v>19.10337829589844</v>
+        <v>19.10337448120117</v>
       </c>
       <c r="C36" t="n">
         <v>36</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B37" t="n">
-        <v>18.25593376159668</v>
+        <v>18.25593566894531</v>
       </c>
       <c r="C37" t="n">
         <v>34.0099983215332</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B38" t="n">
@@ -1191,11 +1203,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B39" t="n">
-        <v>17.44002532958984</v>
+        <v>17.44002723693848</v>
       </c>
       <c r="C39" t="n">
         <v>32.4900016784668</v>
@@ -1216,11 +1228,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B40" t="n">
-        <v>17.75727844238281</v>
+        <v>17.75728034973145</v>
       </c>
       <c r="C40" t="n">
         <v>32.65999984741211</v>
@@ -1241,7 +1253,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B41" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B42" t="n">
@@ -1291,11 +1303,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B43" t="n">
-        <v>19.78752326965332</v>
+        <v>19.78752517700195</v>
       </c>
       <c r="C43" t="n">
         <v>35.97999954223633</v>
@@ -1316,11 +1328,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B44" t="n">
-        <v>22.14134979248047</v>
+        <v>22.1413459777832</v>
       </c>
       <c r="C44" t="n">
         <v>40.2599983215332</v>
@@ -1341,7 +1353,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B45" t="n">
@@ -1366,11 +1378,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B46" t="n">
-        <v>21.52520561218262</v>
+        <v>21.52520942687988</v>
       </c>
       <c r="C46" t="n">
         <v>38.70000076293945</v>
@@ -1391,11 +1403,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B47" t="n">
-        <v>22.99916458129883</v>
+        <v>22.99915313720703</v>
       </c>
       <c r="C47" t="n">
         <v>41.34999847412109</v>
@@ -1416,11 +1428,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B48" t="n">
-        <v>23.53311347961426</v>
+        <v>23.53311920166016</v>
       </c>
       <c r="C48" t="n">
         <v>42.31000137329102</v>
@@ -1441,11 +1453,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B49" t="n">
-        <v>23.08344459533691</v>
+        <v>23.08344268798828</v>
       </c>
       <c r="C49" t="n">
         <v>41.04999923706055</v>
@@ -1466,11 +1478,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B50" t="n">
-        <v>23.06094741821289</v>
+        <v>23.06095314025879</v>
       </c>
       <c r="C50" t="n">
         <v>41.0099983215332</v>
@@ -1491,11 +1503,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B51" t="n">
-        <v>23.65138626098633</v>
+        <v>23.65139961242676</v>
       </c>
       <c r="C51" t="n">
         <v>42.06000137329102</v>
@@ -1516,7 +1528,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B52" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B53" t="n">
@@ -1566,11 +1578,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B54" t="n">
-        <v>21.82515144348145</v>
+        <v>21.82515525817871</v>
       </c>
       <c r="C54" t="n">
         <v>38.38999938964844</v>
@@ -1591,11 +1603,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B55" t="n">
-        <v>19.96831703186035</v>
+        <v>19.96831321716309</v>
       </c>
       <c r="C55" t="n">
         <v>34.63999938964844</v>
@@ -1616,11 +1628,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B56" t="n">
-        <v>18.68282890319824</v>
+        <v>18.68282127380371</v>
       </c>
       <c r="C56" t="n">
         <v>32.40999984741211</v>
@@ -1641,11 +1653,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B57" t="n">
-        <v>15.95620918273926</v>
+        <v>15.95620346069336</v>
       </c>
       <c r="C57" t="n">
         <v>27.68000030517578</v>
@@ -1666,11 +1678,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B58" t="n">
-        <v>16.0612621307373</v>
+        <v>16.0612678527832</v>
       </c>
       <c r="C58" t="n">
         <v>27.35000038146973</v>
@@ -1691,11 +1703,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B59" t="n">
-        <v>13.84146022796631</v>
+        <v>13.84146499633789</v>
       </c>
       <c r="C59" t="n">
         <v>23.56999969482422</v>
@@ -1716,7 +1728,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B60" t="n">
@@ -1741,11 +1753,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B61" t="n">
-        <v>9.745920181274414</v>
+        <v>9.745916366577148</v>
       </c>
       <c r="C61" t="n">
         <v>16.45000076293945</v>
@@ -1766,11 +1778,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B62" t="n">
-        <v>10.7175464630127</v>
+        <v>10.71754837036133</v>
       </c>
       <c r="C62" t="n">
         <v>18.09000015258789</v>
@@ -1795,11 +1807,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B63" t="n">
-        <v>10.5812816619873</v>
+        <v>10.58128261566162</v>
       </c>
       <c r="C63" t="n">
         <v>17.86000061035156</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B64" t="n">
-        <v>10.59444141387939</v>
+        <v>10.59444522857666</v>
       </c>
       <c r="C64" t="n">
         <v>17.76000022888184</v>
@@ -1853,11 +1865,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B65" t="n">
-        <v>10.78533554077148</v>
+        <v>10.7853364944458</v>
       </c>
       <c r="C65" t="n">
         <v>18.07999992370605</v>
@@ -1882,11 +1894,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B66" t="n">
-        <v>11.16711521148682</v>
+        <v>11.1671142578125</v>
       </c>
       <c r="C66" t="n">
         <v>18.71999931335449</v>
@@ -1911,11 +1923,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B67" t="n">
-        <v>12.20286464691162</v>
+        <v>12.20286273956299</v>
       </c>
       <c r="C67" t="n">
         <v>20.32999992370605</v>
@@ -1940,11 +1952,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B68" t="n">
-        <v>13.11522579193115</v>
+        <v>13.1152286529541</v>
       </c>
       <c r="C68" t="n">
         <v>21.85000038146973</v>
@@ -1969,11 +1981,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B69" t="n">
-        <v>13.8835277557373</v>
+        <v>13.8835334777832</v>
       </c>
       <c r="C69" t="n">
         <v>23.1299991607666</v>
@@ -1998,7 +2010,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B70" t="n">
@@ -2025,11 +2037,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B71" t="n">
-        <v>13.40521335601807</v>
+        <v>13.4052152633667</v>
       </c>
       <c r="C71" t="n">
         <v>22.20000076293945</v>
@@ -2052,11 +2064,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B72" t="n">
-        <v>12.5054988861084</v>
+        <v>12.50549697875977</v>
       </c>
       <c r="C72" t="n">
         <v>20.70999908447266</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B73" t="n">
-        <v>13.56551837921143</v>
+        <v>13.56552410125732</v>
       </c>
       <c r="C73" t="n">
         <v>22.34000015258789</v>
@@ -2106,7 +2118,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B74" t="n">
@@ -2135,11 +2147,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B75" t="n">
-        <v>13.20118522644043</v>
+        <v>13.20118618011475</v>
       </c>
       <c r="C75" t="n">
         <v>21.73999977111816</v>
@@ -2164,11 +2176,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B76" t="n">
-        <v>12.60245895385742</v>
+        <v>12.60246086120605</v>
       </c>
       <c r="C76" t="n">
         <v>20.6299991607666</v>
@@ -2193,11 +2205,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B77" t="n">
-        <v>11.46011161804199</v>
+        <v>11.46011066436768</v>
       </c>
       <c r="C77" t="n">
         <v>18.76000022888184</v>
@@ -2222,11 +2234,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B78" t="n">
-        <v>11.70446395874023</v>
+        <v>11.70446586608887</v>
       </c>
       <c r="C78" t="n">
         <v>19.15999984741211</v>
@@ -2251,11 +2263,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B79" t="n">
-        <v>12.55745315551758</v>
+        <v>12.55745410919189</v>
       </c>
       <c r="C79" t="n">
         <v>20.43000030517578</v>
@@ -2280,11 +2292,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B80" t="n">
-        <v>11.88133239746094</v>
+        <v>11.88133144378662</v>
       </c>
       <c r="C80" t="n">
         <v>19.32999992370605</v>
@@ -2309,11 +2321,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B81" t="n">
-        <v>11.78913402557373</v>
+        <v>11.78913593292236</v>
       </c>
       <c r="C81" t="n">
         <v>19.18000030517578</v>
@@ -2338,7 +2350,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B82" t="n">
@@ -2367,11 +2379,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B83" t="n">
-        <v>10.6644868850708</v>
+        <v>10.66448497772217</v>
       </c>
       <c r="C83" t="n">
         <v>17.22999954223633</v>
@@ -2396,11 +2408,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B84" t="n">
-        <v>11.18440246582031</v>
+        <v>11.18440437316895</v>
       </c>
       <c r="C84" t="n">
         <v>18.06999969482422</v>
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B85" t="n">
@@ -2454,11 +2466,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B86" t="n">
-        <v>10.09441375732422</v>
+        <v>10.09440898895264</v>
       </c>
       <c r="C86" t="n">
         <v>16.20000076293945</v>
@@ -2483,11 +2495,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B87" t="n">
-        <v>9.384062767028809</v>
+        <v>9.384061813354492</v>
       </c>
       <c r="C87" t="n">
         <v>15.0600004196167</v>
@@ -2512,7 +2524,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B88" t="n">
@@ -2541,11 +2553,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B89" t="n">
-        <v>10.52326011657715</v>
+        <v>10.5232572555542</v>
       </c>
       <c r="C89" t="n">
         <v>16.68000030517578</v>
@@ -2570,7 +2582,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B90" t="n">
@@ -2599,11 +2611,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B91" t="n">
-        <v>11.34398746490479</v>
+        <v>11.34398937225342</v>
       </c>
       <c r="C91" t="n">
         <v>17.78000068664551</v>
@@ -2626,11 +2638,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B92" t="n">
-        <v>11.29294681549072</v>
+        <v>11.29294776916504</v>
       </c>
       <c r="C92" t="n">
         <v>17.70000076293945</v>
@@ -2653,11 +2665,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B93" t="n">
-        <v>11.31208801269531</v>
+        <v>11.31208515167236</v>
       </c>
       <c r="C93" t="n">
         <v>17.72999954223633</v>
@@ -2680,7 +2692,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B94" t="n">
@@ -2707,11 +2719,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B95" t="n">
-        <v>11.02495384216309</v>
+        <v>11.02495574951172</v>
       </c>
       <c r="C95" t="n">
         <v>17.06999969482422</v>
@@ -2734,11 +2746,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B96" t="n">
-        <v>9.933441162109375</v>
+        <v>9.933438301086426</v>
       </c>
       <c r="C96" t="n">
         <v>15.38000011444092</v>
@@ -2761,7 +2773,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B97" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B98" t="n">
@@ -2817,11 +2829,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B99" t="n">
-        <v>13.0686092376709</v>
+        <v>13.06861209869385</v>
       </c>
       <c r="C99" t="n">
         <v>20.01000022888184</v>
@@ -2846,11 +2858,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B100" t="n">
-        <v>13.13955402374268</v>
+        <v>13.13955307006836</v>
       </c>
       <c r="C100" t="n">
         <v>19.8700008392334</v>
@@ -2875,11 +2887,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B101" t="n">
-        <v>13.1924524307251</v>
+        <v>13.19245529174805</v>
       </c>
       <c r="C101" t="n">
         <v>19.95000076293945</v>
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B102" t="n">
@@ -2933,11 +2945,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B103" t="n">
-        <v>13.80066680908203</v>
+        <v>13.80066871643066</v>
       </c>
       <c r="C103" t="n">
         <v>20.6200008392334</v>
@@ -2962,11 +2974,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B104" t="n">
-        <v>13.56641674041748</v>
+        <v>13.56641864776611</v>
       </c>
       <c r="C104" t="n">
         <v>20.27000045776367</v>
@@ -2991,11 +3003,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B105" t="n">
-        <v>13.79397392272949</v>
+        <v>13.79397678375244</v>
       </c>
       <c r="C105" t="n">
         <v>20.61000061035156</v>
@@ -3020,11 +3032,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B106" t="n">
-        <v>13.54015254974365</v>
+        <v>13.5401496887207</v>
       </c>
       <c r="C106" t="n">
         <v>19.97999954223633</v>
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B107" t="n">
@@ -3078,11 +3090,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B108" t="n">
-        <v>14.34659576416016</v>
+        <v>14.34659862518311</v>
       </c>
       <c r="C108" t="n">
         <v>21.17000007629395</v>
@@ -3107,11 +3119,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B109" t="n">
-        <v>14.31031227111816</v>
+        <v>14.31031036376953</v>
       </c>
       <c r="C109" t="n">
         <v>20.8700008392334</v>
@@ -3136,11 +3148,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B110" t="n">
-        <v>13.14464092254639</v>
+        <v>13.1446418762207</v>
       </c>
       <c r="C110" t="n">
         <v>19.17000007629395</v>
@@ -3165,11 +3177,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B111" t="n">
-        <v>9.544779777526855</v>
+        <v>9.544776916503906</v>
       </c>
       <c r="C111" t="n">
         <v>13.92000007629395</v>
@@ -3194,11 +3206,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B112" t="n">
-        <v>10.44302749633789</v>
+        <v>10.44303035736084</v>
       </c>
       <c r="C112" t="n">
         <v>15.22999954223633</v>
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B113" t="n">
@@ -3248,11 +3260,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B114" t="n">
-        <v>10.58466911315918</v>
+        <v>10.58466815948486</v>
       </c>
       <c r="C114" t="n">
         <v>15.17000007629395</v>
@@ -3273,11 +3285,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B115" t="n">
-        <v>10.02216053009033</v>
+        <v>10.02215671539307</v>
       </c>
       <c r="C115" t="n">
         <v>14.10000038146973</v>
@@ -3298,7 +3310,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B116" t="n">
@@ -3323,11 +3335,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B117" t="n">
-        <v>8.764057159423828</v>
+        <v>8.764056205749512</v>
       </c>
       <c r="C117" t="n">
         <v>12.32999992370605</v>
@@ -3348,11 +3360,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B118" t="n">
-        <v>8.646986961364746</v>
+        <v>8.646989822387695</v>
       </c>
       <c r="C118" t="n">
         <v>11.89999961853027</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B119" t="n">
-        <v>10.44904518127441</v>
+        <v>10.44904613494873</v>
       </c>
       <c r="C119" t="n">
         <v>14.38000011444092</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B120" t="n">
-        <v>9.933135986328125</v>
+        <v>9.933135032653809</v>
       </c>
       <c r="C120" t="n">
         <v>13.67000007629395</v>
@@ -3423,11 +3435,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B121" t="n">
-        <v>10.41756820678711</v>
+        <v>10.41756534576416</v>
       </c>
       <c r="C121" t="n">
         <v>14.07999992370605</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B122" t="n">
-        <v>10.87629413604736</v>
+        <v>10.87629508972168</v>
       </c>
       <c r="C122" t="n">
         <v>14.69999980926514</v>
@@ -3473,11 +3485,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B123" t="n">
-        <v>12.31906604766846</v>
+        <v>12.31906986236572</v>
       </c>
       <c r="C123" t="n">
         <v>16.64999961853027</v>
@@ -3498,7 +3510,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B124" t="n">
@@ -3523,11 +3535,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B125" t="n">
-        <v>13.78285121917725</v>
+        <v>13.78285598754883</v>
       </c>
       <c r="C125" t="n">
         <v>18.34000015258789</v>
@@ -3548,11 +3560,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B126" t="n">
-        <v>13.70018768310547</v>
+        <v>13.7001838684082</v>
       </c>
       <c r="C126" t="n">
         <v>18.22999954223633</v>
@@ -3573,11 +3585,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B127" t="n">
-        <v>13.26142692565918</v>
+        <v>13.26142883300781</v>
       </c>
       <c r="C127" t="n">
         <v>17.3799991607666</v>
@@ -3598,11 +3610,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B128" t="n">
-        <v>12.41446781158447</v>
+        <v>12.41446495056152</v>
       </c>
       <c r="C128" t="n">
         <v>16.27000045776367</v>
@@ -3623,11 +3635,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B129" t="n">
-        <v>12.76545906066895</v>
+        <v>12.76546192169189</v>
       </c>
       <c r="C129" t="n">
         <v>16.72999954223633</v>
@@ -3648,11 +3660,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B130" t="n">
-        <v>12.98275661468506</v>
+        <v>12.98275756835938</v>
       </c>
       <c r="C130" t="n">
         <v>16.75</v>
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B131" t="n">
-        <v>11.98289012908936</v>
+        <v>11.98289203643799</v>
       </c>
       <c r="C131" t="n">
         <v>15.46000003814697</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B132" t="n">
-        <v>12.29292583465576</v>
+        <v>12.29292774200439</v>
       </c>
       <c r="C132" t="n">
         <v>15.85999965667725</v>
@@ -3723,11 +3735,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B133" t="n">
-        <v>13.66666126251221</v>
+        <v>13.66666030883789</v>
       </c>
       <c r="C133" t="n">
         <v>17.36000061035156</v>
@@ -3748,11 +3760,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B134" t="n">
-        <v>13.69814682006836</v>
+        <v>13.69815063476562</v>
       </c>
       <c r="C134" t="n">
         <v>17.39999961853027</v>
@@ -3777,7 +3789,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B135" t="n">
@@ -3806,11 +3818,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B136" t="n">
-        <v>14.50293064117432</v>
+        <v>14.50293159484863</v>
       </c>
       <c r="C136" t="n">
         <v>18.14999961853027</v>
@@ -3835,11 +3847,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B137" t="n">
-        <v>15.73348140716553</v>
+        <v>15.73348331451416</v>
       </c>
       <c r="C137" t="n">
         <v>19.69000053405762</v>
@@ -3864,11 +3876,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B138" t="n">
-        <v>13.39224243164062</v>
+        <v>13.39223957061768</v>
       </c>
       <c r="C138" t="n">
         <v>16.76000022888184</v>
@@ -3893,11 +3905,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B139" t="n">
-        <v>14.60007476806641</v>
+        <v>14.60006999969482</v>
       </c>
       <c r="C139" t="n">
         <v>17.98999977111816</v>
@@ -3922,11 +3934,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B140" t="n">
-        <v>14.86789035797119</v>
+        <v>14.86788749694824</v>
       </c>
       <c r="C140" t="n">
         <v>18.31999969482422</v>
@@ -3951,11 +3963,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B141" t="n">
-        <v>13.5044584274292</v>
+        <v>13.50445747375488</v>
       </c>
       <c r="C141" t="n">
         <v>16.63999938964844</v>
@@ -3980,11 +3992,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B142" t="n">
-        <v>14.93639183044434</v>
+        <v>14.9363899230957</v>
       </c>
       <c r="C142" t="n">
         <v>18.1200008392334</v>
@@ -4009,7 +4021,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B143" t="n">
@@ -4038,11 +4050,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B144" t="n">
-        <v>14.90341854095459</v>
+        <v>14.90342140197754</v>
       </c>
       <c r="C144" t="n">
         <v>18.07999992370605</v>
@@ -4067,11 +4079,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B145" t="n">
-        <v>15.31289958953857</v>
+        <v>15.31289768218994</v>
       </c>
       <c r="C145" t="n">
         <v>18.29999923706055</v>
@@ -4096,11 +4108,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B146" t="n">
-        <v>14.27530193328857</v>
+        <v>14.27530384063721</v>
       </c>
       <c r="C146" t="n">
         <v>17.05999946594238</v>
@@ -4125,11 +4137,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B147" t="n">
-        <v>14.65184783935547</v>
+        <v>14.65185070037842</v>
       </c>
       <c r="C147" t="n">
         <v>17.51000022888184</v>
@@ -4154,11 +4166,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B148" t="n">
-        <v>14.58898830413818</v>
+        <v>14.58899021148682</v>
       </c>
       <c r="C148" t="n">
         <v>17.14999961853027</v>
@@ -4183,7 +4195,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B149" t="n">
@@ -4212,11 +4224,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B150" t="n">
-        <v>14.64853382110596</v>
+        <v>14.64853477478027</v>
       </c>
       <c r="C150" t="n">
         <v>17.21999931335449</v>
@@ -4241,11 +4253,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B151" t="n">
-        <v>15.30875492095947</v>
+        <v>15.30875682830811</v>
       </c>
       <c r="C151" t="n">
         <v>17.70999908447266</v>
@@ -4270,11 +4282,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B152" t="n">
-        <v>14.88519287109375</v>
+        <v>14.88519191741943</v>
       </c>
       <c r="C152" t="n">
         <v>17.21999931335449</v>
@@ -4299,11 +4311,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B153" t="n">
-        <v>14.33196926116943</v>
+        <v>14.33196830749512</v>
       </c>
       <c r="C153" t="n">
         <v>16.57999992370605</v>
@@ -4328,11 +4340,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B154" t="n">
-        <v>14.24984073638916</v>
+        <v>14.24983978271484</v>
       </c>
       <c r="C154" t="n">
         <v>16.20000076293945</v>
@@ -4357,7 +4369,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B155" t="n">
@@ -4386,11 +4398,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B156" t="n">
-        <v>15.51648998260498</v>
+        <v>15.5164909362793</v>
       </c>
       <c r="C156" t="n">
         <v>17.63999938964844</v>
@@ -4415,11 +4427,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B157" t="n">
-        <v>15.12966442108154</v>
+        <v>15.12966346740723</v>
       </c>
       <c r="C157" t="n">
         <v>16.92000007629395</v>
@@ -4444,11 +4456,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B158" t="n">
-        <v>15.54993057250977</v>
+        <v>15.54993343353271</v>
       </c>
       <c r="C158" t="n">
         <v>17.38999938964844</v>
@@ -4473,7 +4485,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B159" t="n">
@@ -4502,11 +4514,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B160" t="n">
-        <v>16.60172271728516</v>
+        <v>16.60171890258789</v>
       </c>
       <c r="C160" t="n">
         <v>18.28000068664551</v>
@@ -4531,11 +4543,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B161" t="n">
-        <v>17.70063018798828</v>
+        <v>17.70062828063965</v>
       </c>
       <c r="C161" t="n">
         <v>19.48999977111816</v>
@@ -4560,11 +4572,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B162" t="n">
-        <v>18.04574584960938</v>
+        <v>18.04574394226074</v>
       </c>
       <c r="C162" t="n">
         <v>19.8700008392334</v>
@@ -4589,7 +4601,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B163" t="n">
@@ -4618,11 +4630,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B164" t="n">
-        <v>19.8529052734375</v>
+        <v>19.85290908813477</v>
       </c>
       <c r="C164" t="n">
         <v>21.56999969482422</v>
@@ -4647,11 +4659,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B165" t="n">
-        <v>20.33151054382324</v>
+        <v>20.33151245117188</v>
       </c>
       <c r="C165" t="n">
         <v>22.09000015258789</v>
@@ -4676,7 +4688,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B166" t="n">
@@ -4705,11 +4717,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B167" t="n">
-        <v>26.32476615905762</v>
+        <v>26.32476806640625</v>
       </c>
       <c r="C167" t="n">
         <v>28.27000045776367</v>
@@ -4734,11 +4746,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B168" t="n">
-        <v>25.51462554931641</v>
+        <v>25.51462936401367</v>
       </c>
       <c r="C168" t="n">
         <v>27.39999961853027</v>
@@ -4763,7 +4775,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B169" t="n">
@@ -4792,11 +4804,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B170" t="n">
-        <v>25.5025463104248</v>
+        <v>25.50254821777344</v>
       </c>
       <c r="C170" t="n">
         <v>27.10000038146973</v>
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B171" t="n">
@@ -4850,11 +4862,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B172" t="n">
-        <v>25.01910972595215</v>
+        <v>25.01911163330078</v>
       </c>
       <c r="C172" t="n">
         <v>26.29999923706055</v>
@@ -4879,7 +4891,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B173" t="n">
@@ -4908,11 +4920,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B174" t="n">
-        <v>27.9681339263916</v>
+        <v>27.96813201904297</v>
       </c>
       <c r="C174" t="n">
         <v>29.39999961853027</v>
@@ -4937,11 +4949,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B175" t="n">
-        <v>26.9755744934082</v>
+        <v>26.97557258605957</v>
       </c>
       <c r="C175" t="n">
         <v>28.05999946594238</v>
@@ -4966,11 +4978,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B176" t="n">
-        <v>25.93731498718262</v>
+        <v>25.93731307983398</v>
       </c>
       <c r="C176" t="n">
         <v>26.97999954223633</v>
@@ -4995,7 +5007,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B177" t="n">
@@ -5024,7 +5036,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B178" t="n">
@@ -5053,7 +5065,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B179" t="n">
@@ -5082,7 +5094,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B180" t="n">
@@ -5111,11 +5123,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B181" t="n">
-        <v>29.64329719543457</v>
+        <v>29.6432991027832</v>
       </c>
       <c r="C181" t="n">
         <v>30.48999977111816</v>
@@ -5140,7 +5152,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B182" t="n">
@@ -5169,7 +5181,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B183" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B184" t="n">
@@ -5227,7 +5239,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B185" t="n">
@@ -5256,7 +5268,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B186" t="n">
@@ -5285,7 +5297,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B187" t="n">
@@ -5314,7 +5326,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B188" t="n">
@@ -5343,32 +5355,32 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B189" t="n">
-        <v>31.3700008392334</v>
+        <v>31.25</v>
       </c>
       <c r="C189" t="n">
-        <v>31.3700008392334</v>
+        <v>31.25</v>
       </c>
       <c r="D189" t="n">
-        <v>214104900</v>
+        <v>221789800</v>
       </c>
       <c r="E189" t="n">
         <v>1.56</v>
       </c>
       <c r="F189" t="n">
-        <v>20.10897489694448</v>
+        <v>20.03205128205128</v>
       </c>
       <c r="G189" t="n">
         <v>2226802089</v>
       </c>
       <c r="H189" t="n">
-        <v>69854783400.73668</v>
+        <v>69587565281.25</v>
       </c>
       <c r="I189" t="n">
-        <v>0.09614904757707904</v>
+        <v>0.09960014008231874</v>
       </c>
     </row>
   </sheetData>
@@ -5400,75 +5412,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5504,13 +5516,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5546,13 +5558,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5588,13 +5600,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5621,7 +5633,7 @@
       <c r="I5" t="n">
         <v>1.196254826254826</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K5" t="n">
@@ -5634,13 +5646,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5667,7 +5679,7 @@
       <c r="I6" t="n">
         <v>0.8899999999999999</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K6" t="n">
@@ -5680,13 +5692,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5713,7 +5725,7 @@
       <c r="I7" t="n">
         <v>0.8099999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K7" t="n">
@@ -5726,13 +5738,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5759,7 +5771,7 @@
       <c r="I8" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K8" t="n">
@@ -5772,13 +5784,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5805,7 +5817,7 @@
       <c r="I9" t="n">
         <v>0.4499999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K9" t="n">
@@ -5818,13 +5830,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5851,7 +5863,7 @@
       <c r="I10" t="n">
         <v>0.1</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K10" t="n">
@@ -5864,13 +5876,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5897,7 +5909,7 @@
       <c r="I11" t="n">
         <v>0.02000000000000002</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="K11" t="n">
@@ -5910,13 +5922,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5943,7 +5955,7 @@
       <c r="I12" t="n">
         <v>0.02000000000000002</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="K12" t="n">
@@ -5956,13 +5968,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5989,7 +6001,7 @@
       <c r="I13" t="n">
         <v>-0.16</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="K13" t="n">
@@ -6002,13 +6014,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6035,7 +6047,7 @@
       <c r="I14" t="n">
         <v>0.2499999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="K14" t="n">
@@ -6048,13 +6060,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6081,7 +6093,7 @@
       <c r="I15" t="n">
         <v>0.3099999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="K15" t="n">
@@ -6094,13 +6106,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42940</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6127,7 +6139,7 @@
       <c r="I16" t="n">
         <v>0.3099999999999999</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42940</v>
       </c>
       <c r="K16" t="n">
@@ -6140,13 +6152,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6173,7 +6185,7 @@
       <c r="I17" t="n">
         <v>0.5599999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="K17" t="n">
@@ -6186,13 +6198,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6219,7 +6231,7 @@
       <c r="I18" t="n">
         <v>0.01000000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K18" t="n">
@@ -6232,13 +6244,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6265,7 +6277,7 @@
       <c r="I19" t="n">
         <v>0.05000000000000002</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K19" t="n">
@@ -6278,13 +6290,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6311,7 +6323,7 @@
       <c r="I20" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="K20" t="n">
@@ -6324,13 +6336,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6357,7 +6369,7 @@
       <c r="I21" t="n">
         <v>-0.01999999999999996</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="K21" t="n">
@@ -6370,13 +6382,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6403,7 +6415,7 @@
       <c r="I22" t="n">
         <v>0.66</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="K22" t="n">
@@ -6416,13 +6428,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6449,7 +6461,7 @@
       <c r="I23" t="n">
         <v>0.68</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="K23" t="n">
@@ -6462,13 +6474,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6495,7 +6507,7 @@
       <c r="I24" t="n">
         <v>0.99</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="K24" t="n">
@@ -6508,13 +6520,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6541,7 +6553,7 @@
       <c r="I25" t="n">
         <v>0.8999999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="K25" t="n">
@@ -6554,13 +6566,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6587,7 +6599,7 @@
       <c r="I26" t="n">
         <v>0.96</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K26" t="n">
@@ -6600,13 +6612,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6633,7 +6645,7 @@
       <c r="I27" t="n">
         <v>0.5800000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K27" t="n">
@@ -6646,13 +6658,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6679,7 +6691,7 @@
       <c r="I28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K28" t="n">
@@ -6692,13 +6704,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6725,7 +6737,7 @@
       <c r="I29" t="n">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K29" t="n">
@@ -6738,13 +6750,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6771,7 +6783,7 @@
       <c r="I30" t="n">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K30" t="n">
@@ -6784,13 +6796,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6817,7 +6829,7 @@
       <c r="I31" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K31" t="n">
@@ -6830,13 +6842,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6863,7 +6875,7 @@
       <c r="I32" t="n">
         <v>0.75</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K32" t="n">
@@ -6876,13 +6888,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6909,7 +6921,7 @@
       <c r="I33" t="n">
         <v>0.77</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K33" t="n">
@@ -6922,13 +6934,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6955,7 +6967,7 @@
       <c r="I34" t="n">
         <v>0.78</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K34" t="n">
@@ -6968,13 +6980,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7001,7 +7013,7 @@
       <c r="I35" t="n">
         <v>0.45</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K35" t="n">
@@ -7014,13 +7026,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7047,7 +7059,7 @@
       <c r="I36" t="n">
         <v>1.07</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="K36" t="n">
@@ -7060,13 +7072,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7093,7 +7105,7 @@
       <c r="I37" t="n">
         <v>1.1</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="K37" t="n">
@@ -7106,13 +7118,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7139,7 +7151,7 @@
       <c r="I38" t="n">
         <v>1.12</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="K38" t="n">
@@ -7152,13 +7164,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7185,7 +7197,7 @@
       <c r="I39" t="n">
         <v>1.13</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="K39" t="n">
@@ -7198,13 +7210,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7231,7 +7243,7 @@
       <c r="I40" t="n">
         <v>1.11</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="K40" t="n">
@@ -7244,13 +7256,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7277,7 +7289,7 @@
       <c r="I41" t="n">
         <v>1.1</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="K41" t="n">
@@ -7290,13 +7302,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7323,7 +7335,7 @@
       <c r="I42" t="n">
         <v>1.06</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K42" t="n">
@@ -7336,13 +7348,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7369,7 +7381,7 @@
       <c r="I43" t="n">
         <v>1.09</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="K43" t="n">
@@ -7382,13 +7394,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7415,7 +7427,7 @@
       <c r="I44" t="n">
         <v>1.09</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="K44" t="n">
@@ -7428,13 +7440,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7461,7 +7473,7 @@
       <c r="I45" t="n">
         <v>1.13</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="K45" t="n">
@@ -7474,13 +7486,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7507,7 +7519,7 @@
       <c r="I46" t="n">
         <v>1.17</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K46" t="n">
@@ -7520,13 +7532,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7553,7 +7565,7 @@
       <c r="I47" t="n">
         <v>1.16</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="K47" t="n">
@@ -7566,13 +7578,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7599,7 +7611,7 @@
       <c r="I48" t="n">
         <v>1.22</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="K48" t="n">
@@ -7612,13 +7624,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7645,7 +7657,7 @@
       <c r="I49" t="n">
         <v>1.22</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K49" t="n">
@@ -7658,13 +7670,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7691,7 +7703,7 @@
       <c r="I50" t="n">
         <v>1.37</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K50" t="n">
@@ -7704,13 +7716,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7737,7 +7749,7 @@
       <c r="I51" t="n">
         <v>1.49</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K51" t="n">
@@ -7750,13 +7762,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7783,7 +7795,7 @@
       <c r="I52" t="n">
         <v>1.56</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K52" t="n">
@@ -7820,52 +7832,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C2" t="n">
@@ -7894,10 +7906,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C3" t="n">
@@ -7926,10 +7938,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C4" t="n">
@@ -7958,10 +7970,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41936</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C5" t="n">
@@ -7990,10 +8002,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42037</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42058</v>
       </c>
       <c r="C6" t="n">
@@ -8022,10 +8034,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C7" t="n">
@@ -8054,10 +8066,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42208</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="C8" t="n">
@@ -8086,10 +8098,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42298</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C9" t="n">
@@ -8118,10 +8130,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42411</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="C10" t="n">
@@ -8150,10 +8162,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42481</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="C11" t="n">
@@ -8182,10 +8194,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42572</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="C12" t="n">
@@ -8214,10 +8226,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42663</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="C13" t="n">
@@ -8246,10 +8258,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42775</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="C14" t="n">
@@ -8278,10 +8290,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42845</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="C15" t="n">
@@ -8310,10 +8322,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42936</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42940</v>
       </c>
       <c r="C16" t="n">
@@ -8342,10 +8354,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43027</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="C17" t="n">
@@ -8374,10 +8386,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43139</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C18" t="n">
@@ -8406,10 +8418,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C19" t="n">
@@ -8438,10 +8450,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43300</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="C20" t="n">
@@ -8470,10 +8482,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43391</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="C21" t="n">
@@ -8502,10 +8514,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43503</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="C22" t="n">
@@ -8534,10 +8546,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="C23" t="n">
@@ -8566,10 +8578,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43658</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="C24" t="n">
@@ -8598,10 +8610,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43755</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43759</v>
       </c>
       <c r="C25" t="n">
@@ -8630,10 +8642,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C26" t="n">
@@ -8662,10 +8674,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C27" t="n">
@@ -8694,10 +8706,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44035</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44039</v>
       </c>
       <c r="C28" t="n">
@@ -8726,10 +8738,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C29" t="n">
@@ -8758,10 +8770,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44231</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C30" t="n">
@@ -8790,10 +8802,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="C31" t="n">
@@ -8822,10 +8834,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44399</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="C32" t="n">
@@ -8854,10 +8866,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="C33" t="n">
@@ -8886,10 +8898,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="C34" t="n">
@@ -8918,10 +8930,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44672</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C35" t="n">
@@ -8950,10 +8962,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44763</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="C36" t="n">
@@ -8982,10 +8994,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="C37" t="n">
@@ -9014,10 +9026,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44964</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="C38" t="n">
@@ -9046,10 +9058,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="C39" t="n">
@@ -9078,10 +9090,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45127</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="C40" t="n">
@@ -9110,10 +9122,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45218</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="C41" t="n">
@@ -9142,10 +9154,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C42" t="n">
@@ -9174,10 +9186,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="C43" t="n">
@@ -9206,10 +9218,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="C44" t="n">
@@ -9238,10 +9250,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45582</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="C45" t="n">
@@ -9270,10 +9282,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45700</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C46" t="n">
@@ -9302,10 +9314,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="C47" t="n">
@@ -9334,10 +9346,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="C48" t="n">
@@ -9366,10 +9378,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C49" t="n">
@@ -9398,10 +9410,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C50" t="n">
@@ -9430,10 +9442,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C51" t="n">
@@ -9462,10 +9474,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46226</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C52" t="n">
@@ -9512,12 +9524,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/KMI.xlsx
+++ b/salidas/empresas/KMI.xlsx
@@ -498,7 +498,7 @@
         <v>40602</v>
       </c>
       <c r="B2" t="n">
-        <v>14.56126594543457</v>
+        <v>14.56126689910889</v>
       </c>
       <c r="C2" t="n">
         <v>30.5</v>
@@ -517,7 +517,7 @@
         <v>40633</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15068244934082</v>
+        <v>14.15068435668945</v>
       </c>
       <c r="C3" t="n">
         <v>29.63999938964844</v>
@@ -536,7 +536,7 @@
         <v>40663</v>
       </c>
       <c r="B4" t="n">
-        <v>13.7111349105835</v>
+        <v>13.71113586425781</v>
       </c>
       <c r="C4" t="n">
         <v>28.57999992370605</v>
@@ -555,7 +555,7 @@
         <v>40694</v>
       </c>
       <c r="B5" t="n">
-        <v>14.05175304412842</v>
+        <v>14.0517520904541</v>
       </c>
       <c r="C5" t="n">
         <v>29.29000091552734</v>
@@ -574,7 +574,7 @@
         <v>40724</v>
       </c>
       <c r="B6" t="n">
-        <v>13.78309345245361</v>
+        <v>13.78310012817383</v>
       </c>
       <c r="C6" t="n">
         <v>28.72999954223633</v>
@@ -593,7 +593,7 @@
         <v>40755</v>
       </c>
       <c r="B7" t="n">
-        <v>13.6889476776123</v>
+        <v>13.6889533996582</v>
       </c>
       <c r="C7" t="n">
         <v>28.22999954223633</v>
@@ -612,7 +612,7 @@
         <v>40786</v>
       </c>
       <c r="B8" t="n">
-        <v>12.53487110137939</v>
+        <v>12.53487300872803</v>
       </c>
       <c r="C8" t="n">
         <v>25.85000038146973</v>
@@ -631,7 +631,7 @@
         <v>40816</v>
       </c>
       <c r="B9" t="n">
-        <v>12.55427169799805</v>
+        <v>12.55427646636963</v>
       </c>
       <c r="C9" t="n">
         <v>25.88999938964844</v>
@@ -650,7 +650,7 @@
         <v>40847</v>
       </c>
       <c r="B10" t="n">
-        <v>14.01007461547852</v>
+        <v>14.01007270812988</v>
       </c>
       <c r="C10" t="n">
         <v>28.60000038146973</v>
@@ -669,7 +669,7 @@
         <v>40877</v>
       </c>
       <c r="B11" t="n">
-        <v>14.45095348358154</v>
+        <v>14.45095443725586</v>
       </c>
       <c r="C11" t="n">
         <v>29.5</v>
@@ -688,7 +688,7 @@
         <v>40908</v>
       </c>
       <c r="B12" t="n">
-        <v>15.75888919830322</v>
+        <v>15.75887966156006</v>
       </c>
       <c r="C12" t="n">
         <v>32.16999816894531</v>
@@ -707,7 +707,7 @@
         <v>40939</v>
       </c>
       <c r="B13" t="n">
-        <v>16.05742073059082</v>
+        <v>16.05741882324219</v>
       </c>
       <c r="C13" t="n">
         <v>32.47000122070312</v>
@@ -726,7 +726,7 @@
         <v>40968</v>
       </c>
       <c r="B14" t="n">
-        <v>17.42727470397949</v>
+        <v>17.42727851867676</v>
       </c>
       <c r="C14" t="n">
         <v>35.2400016784668</v>
@@ -745,7 +745,7 @@
         <v>40999</v>
       </c>
       <c r="B15" t="n">
-        <v>19.11362838745117</v>
+        <v>19.11362266540527</v>
       </c>
       <c r="C15" t="n">
         <v>38.65000152587891</v>
@@ -764,7 +764,7 @@
         <v>41029</v>
       </c>
       <c r="B16" t="n">
-        <v>17.91324424743652</v>
+        <v>17.91324615478516</v>
       </c>
       <c r="C16" t="n">
         <v>35.90000152587891</v>
@@ -783,7 +783,7 @@
         <v>41060</v>
       </c>
       <c r="B17" t="n">
-        <v>17.05999755859375</v>
+        <v>17.05999946594238</v>
       </c>
       <c r="C17" t="n">
         <v>34.18999862670898</v>
@@ -802,7 +802,7 @@
         <v>41090</v>
       </c>
       <c r="B18" t="n">
-        <v>16.07701110839844</v>
+        <v>16.0770149230957</v>
       </c>
       <c r="C18" t="n">
         <v>32.22000122070312</v>
@@ -821,7 +821,7 @@
         <v>41121</v>
       </c>
       <c r="B19" t="n">
-        <v>18.0451545715332</v>
+        <v>18.04515266418457</v>
       </c>
       <c r="C19" t="n">
         <v>35.81000137329102</v>
@@ -840,7 +840,7 @@
         <v>41152</v>
       </c>
       <c r="B20" t="n">
-        <v>18.02499771118164</v>
+        <v>18.02499961853027</v>
       </c>
       <c r="C20" t="n">
         <v>35.77000045776367</v>
@@ -859,7 +859,7 @@
         <v>41182</v>
       </c>
       <c r="B21" t="n">
-        <v>17.89902305603027</v>
+        <v>17.89902114868164</v>
       </c>
       <c r="C21" t="n">
         <v>35.52000045776367</v>
@@ -878,7 +878,7 @@
         <v>41213</v>
       </c>
       <c r="B22" t="n">
-        <v>17.67421340942383</v>
+        <v>17.67422103881836</v>
       </c>
       <c r="C22" t="n">
         <v>34.70999908447266</v>
@@ -897,7 +897,7 @@
         <v>41243</v>
       </c>
       <c r="B23" t="n">
-        <v>17.21593284606934</v>
+        <v>17.2159366607666</v>
       </c>
       <c r="C23" t="n">
         <v>33.81000137329102</v>
@@ -916,7 +916,7 @@
         <v>41274</v>
       </c>
       <c r="B24" t="n">
-        <v>17.98991775512695</v>
+        <v>17.98991203308105</v>
       </c>
       <c r="C24" t="n">
         <v>35.33000183105469</v>
@@ -954,7 +954,7 @@
         <v>41333</v>
       </c>
       <c r="B26" t="n">
-        <v>19.06386375427246</v>
+        <v>19.06386566162109</v>
       </c>
       <c r="C26" t="n">
         <v>37.06999969482422</v>
@@ -973,7 +973,7 @@
         <v>41364</v>
       </c>
       <c r="B27" t="n">
-        <v>19.8918285369873</v>
+        <v>19.8918342590332</v>
       </c>
       <c r="C27" t="n">
         <v>38.68000030517578</v>
@@ -992,7 +992,7 @@
         <v>41394</v>
       </c>
       <c r="B28" t="n">
-        <v>20.3007698059082</v>
+        <v>20.30078125</v>
       </c>
       <c r="C28" t="n">
         <v>39.09999847412109</v>
@@ -1011,7 +1011,7 @@
         <v>41425</v>
       </c>
       <c r="B29" t="n">
-        <v>19.71927261352539</v>
+        <v>19.71926498413086</v>
       </c>
       <c r="C29" t="n">
         <v>37.97999954223633</v>
@@ -1030,7 +1030,7 @@
         <v>41455</v>
       </c>
       <c r="B30" t="n">
-        <v>19.80753707885742</v>
+        <v>19.80752944946289</v>
       </c>
       <c r="C30" t="n">
         <v>38.15000152587891</v>
@@ -1049,7 +1049,7 @@
         <v>41486</v>
       </c>
       <c r="B31" t="n">
-        <v>19.80974388122559</v>
+        <v>19.80974006652832</v>
       </c>
       <c r="C31" t="n">
         <v>37.7599983215332</v>
@@ -1068,7 +1068,7 @@
         <v>41517</v>
       </c>
       <c r="B32" t="n">
-        <v>19.89893531799316</v>
+        <v>19.8989315032959</v>
       </c>
       <c r="C32" t="n">
         <v>37.93000030517578</v>
@@ -1087,7 +1087,7 @@
         <v>41547</v>
       </c>
       <c r="B33" t="n">
-        <v>18.66082000732422</v>
+        <v>18.66082382202148</v>
       </c>
       <c r="C33" t="n">
         <v>35.56999969482422</v>
@@ -1125,7 +1125,7 @@
         <v>41608</v>
       </c>
       <c r="B35" t="n">
-        <v>18.85927772521973</v>
+        <v>18.85927200317383</v>
       </c>
       <c r="C35" t="n">
         <v>35.54000091552734</v>
@@ -1144,7 +1144,7 @@
         <v>41639</v>
       </c>
       <c r="B36" t="n">
-        <v>19.10337448120117</v>
+        <v>19.10337066650391</v>
       </c>
       <c r="C36" t="n">
         <v>36</v>
@@ -1163,7 +1163,7 @@
         <v>41670</v>
       </c>
       <c r="B37" t="n">
-        <v>18.25593566894531</v>
+        <v>18.25593185424805</v>
       </c>
       <c r="C37" t="n">
         <v>34.0099983215332</v>
@@ -1207,7 +1207,7 @@
         <v>41729</v>
       </c>
       <c r="B39" t="n">
-        <v>17.44002723693848</v>
+        <v>17.44002532958984</v>
       </c>
       <c r="C39" t="n">
         <v>32.4900016784668</v>
@@ -1232,7 +1232,7 @@
         <v>41759</v>
       </c>
       <c r="B40" t="n">
-        <v>17.75728034973145</v>
+        <v>17.75728225708008</v>
       </c>
       <c r="C40" t="n">
         <v>32.65999984741211</v>
@@ -1257,7 +1257,7 @@
         <v>41790</v>
       </c>
       <c r="B41" t="n">
-        <v>18.1541862487793</v>
+        <v>18.15417861938477</v>
       </c>
       <c r="C41" t="n">
         <v>33.38999938964844</v>
@@ -1307,7 +1307,7 @@
         <v>41851</v>
       </c>
       <c r="B43" t="n">
-        <v>19.78752517700195</v>
+        <v>19.78752326965332</v>
       </c>
       <c r="C43" t="n">
         <v>35.97999954223633</v>
@@ -1332,7 +1332,7 @@
         <v>41882</v>
       </c>
       <c r="B44" t="n">
-        <v>22.1413459777832</v>
+        <v>22.14134407043457</v>
       </c>
       <c r="C44" t="n">
         <v>40.2599983215332</v>
@@ -1357,7 +1357,7 @@
         <v>41912</v>
       </c>
       <c r="B45" t="n">
-        <v>21.08542633056641</v>
+        <v>21.08542823791504</v>
       </c>
       <c r="C45" t="n">
         <v>38.34000015258789</v>
@@ -1382,7 +1382,7 @@
         <v>41943</v>
       </c>
       <c r="B46" t="n">
-        <v>21.52520942687988</v>
+        <v>21.52521133422852</v>
       </c>
       <c r="C46" t="n">
         <v>38.70000076293945</v>
@@ -1407,7 +1407,7 @@
         <v>41973</v>
       </c>
       <c r="B47" t="n">
-        <v>22.99915313720703</v>
+        <v>22.99915885925293</v>
       </c>
       <c r="C47" t="n">
         <v>41.34999847412109</v>
@@ -1432,7 +1432,7 @@
         <v>42004</v>
       </c>
       <c r="B48" t="n">
-        <v>23.53311920166016</v>
+        <v>23.53311538696289</v>
       </c>
       <c r="C48" t="n">
         <v>42.31000137329102</v>
@@ -1482,7 +1482,7 @@
         <v>42063</v>
       </c>
       <c r="B50" t="n">
-        <v>23.06095314025879</v>
+        <v>23.06094932556152</v>
       </c>
       <c r="C50" t="n">
         <v>41.0099983215332</v>
@@ -1507,7 +1507,7 @@
         <v>42094</v>
       </c>
       <c r="B51" t="n">
-        <v>23.65139961242676</v>
+        <v>23.65138816833496</v>
       </c>
       <c r="C51" t="n">
         <v>42.06000137329102</v>
@@ -1532,7 +1532,7 @@
         <v>42124</v>
       </c>
       <c r="B52" t="n">
-        <v>24.41756629943848</v>
+        <v>24.41756820678711</v>
       </c>
       <c r="C52" t="n">
         <v>42.95000076293945</v>
@@ -1557,7 +1557,7 @@
         <v>42155</v>
       </c>
       <c r="B53" t="n">
-        <v>23.5875415802002</v>
+        <v>23.58754348754883</v>
       </c>
       <c r="C53" t="n">
         <v>41.4900016784668</v>
@@ -1582,7 +1582,7 @@
         <v>42185</v>
       </c>
       <c r="B54" t="n">
-        <v>21.82515525817871</v>
+        <v>21.82515716552734</v>
       </c>
       <c r="C54" t="n">
         <v>38.38999938964844</v>
@@ -1632,7 +1632,7 @@
         <v>42247</v>
       </c>
       <c r="B56" t="n">
-        <v>18.68282127380371</v>
+        <v>18.68282699584961</v>
       </c>
       <c r="C56" t="n">
         <v>32.40999984741211</v>
@@ -1657,7 +1657,7 @@
         <v>42277</v>
       </c>
       <c r="B57" t="n">
-        <v>15.95620346069336</v>
+        <v>15.95620632171631</v>
       </c>
       <c r="C57" t="n">
         <v>27.68000030517578</v>
@@ -1682,7 +1682,7 @@
         <v>42308</v>
       </c>
       <c r="B58" t="n">
-        <v>16.0612678527832</v>
+        <v>16.06126976013184</v>
       </c>
       <c r="C58" t="n">
         <v>27.35000038146973</v>
@@ -1707,7 +1707,7 @@
         <v>42338</v>
       </c>
       <c r="B59" t="n">
-        <v>13.84146499633789</v>
+        <v>13.84145927429199</v>
       </c>
       <c r="C59" t="n">
         <v>23.56999969482422</v>
@@ -1732,7 +1732,7 @@
         <v>42369</v>
       </c>
       <c r="B60" t="n">
-        <v>8.761757850646973</v>
+        <v>8.761756896972656</v>
       </c>
       <c r="C60" t="n">
         <v>14.92000007629395</v>
@@ -1757,7 +1757,7 @@
         <v>42400</v>
       </c>
       <c r="B61" t="n">
-        <v>9.745916366577148</v>
+        <v>9.745919227600098</v>
       </c>
       <c r="C61" t="n">
         <v>16.45000076293945</v>
@@ -1782,7 +1782,7 @@
         <v>42429</v>
       </c>
       <c r="B62" t="n">
-        <v>10.71754837036133</v>
+        <v>10.71754932403564</v>
       </c>
       <c r="C62" t="n">
         <v>18.09000015258789</v>
@@ -1811,7 +1811,7 @@
         <v>42460</v>
       </c>
       <c r="B63" t="n">
-        <v>10.58128261566162</v>
+        <v>10.58128356933594</v>
       </c>
       <c r="C63" t="n">
         <v>17.86000061035156</v>
@@ -1840,7 +1840,7 @@
         <v>42490</v>
       </c>
       <c r="B64" t="n">
-        <v>10.59444522857666</v>
+        <v>10.59444236755371</v>
       </c>
       <c r="C64" t="n">
         <v>17.76000022888184</v>
@@ -1869,7 +1869,7 @@
         <v>42521</v>
       </c>
       <c r="B65" t="n">
-        <v>10.7853364944458</v>
+        <v>10.78533363342285</v>
       </c>
       <c r="C65" t="n">
         <v>18.07999992370605</v>
@@ -1898,7 +1898,7 @@
         <v>42551</v>
       </c>
       <c r="B66" t="n">
-        <v>11.1671142578125</v>
+        <v>11.16711711883545</v>
       </c>
       <c r="C66" t="n">
         <v>18.71999931335449</v>
@@ -1927,7 +1927,7 @@
         <v>42582</v>
       </c>
       <c r="B67" t="n">
-        <v>12.20286273956299</v>
+        <v>12.2028636932373</v>
       </c>
       <c r="C67" t="n">
         <v>20.32999992370605</v>
@@ -1956,7 +1956,7 @@
         <v>42613</v>
       </c>
       <c r="B68" t="n">
-        <v>13.1152286529541</v>
+        <v>13.11522483825684</v>
       </c>
       <c r="C68" t="n">
         <v>21.85000038146973</v>
@@ -1985,7 +1985,7 @@
         <v>42643</v>
       </c>
       <c r="B69" t="n">
-        <v>13.8835334777832</v>
+        <v>13.88352870941162</v>
       </c>
       <c r="C69" t="n">
         <v>23.1299991607666</v>
@@ -2014,7 +2014,7 @@
         <v>42674</v>
       </c>
       <c r="B70" t="n">
-        <v>12.33642101287842</v>
+        <v>12.33641910552979</v>
       </c>
       <c r="C70" t="n">
         <v>20.43000030517578</v>
@@ -2041,7 +2041,7 @@
         <v>42704</v>
       </c>
       <c r="B71" t="n">
-        <v>13.4052152633667</v>
+        <v>13.40521717071533</v>
       </c>
       <c r="C71" t="n">
         <v>22.20000076293945</v>
@@ -2068,7 +2068,7 @@
         <v>42735</v>
       </c>
       <c r="B72" t="n">
-        <v>12.50549697875977</v>
+        <v>12.50549507141113</v>
       </c>
       <c r="C72" t="n">
         <v>20.70999908447266</v>
@@ -2095,7 +2095,7 @@
         <v>42766</v>
       </c>
       <c r="B73" t="n">
-        <v>13.56552410125732</v>
+        <v>13.56552028656006</v>
       </c>
       <c r="C73" t="n">
         <v>22.34000015258789</v>
@@ -2122,7 +2122,7 @@
         <v>42794</v>
       </c>
       <c r="B74" t="n">
-        <v>12.9400749206543</v>
+        <v>12.94007587432861</v>
       </c>
       <c r="C74" t="n">
         <v>21.30999946594238</v>
@@ -2151,7 +2151,7 @@
         <v>42825</v>
       </c>
       <c r="B75" t="n">
-        <v>13.20118618011475</v>
+        <v>13.20118236541748</v>
       </c>
       <c r="C75" t="n">
         <v>21.73999977111816</v>
@@ -2180,7 +2180,7 @@
         <v>42855</v>
       </c>
       <c r="B76" t="n">
-        <v>12.60246086120605</v>
+        <v>12.60245609283447</v>
       </c>
       <c r="C76" t="n">
         <v>20.6299991607666</v>
@@ -2209,7 +2209,7 @@
         <v>42886</v>
       </c>
       <c r="B77" t="n">
-        <v>11.46011066436768</v>
+        <v>11.46011352539062</v>
       </c>
       <c r="C77" t="n">
         <v>18.76000022888184</v>
@@ -2238,7 +2238,7 @@
         <v>42916</v>
       </c>
       <c r="B78" t="n">
-        <v>11.70446586608887</v>
+        <v>11.70446300506592</v>
       </c>
       <c r="C78" t="n">
         <v>19.15999984741211</v>
@@ -2296,7 +2296,7 @@
         <v>42978</v>
       </c>
       <c r="B80" t="n">
-        <v>11.88133144378662</v>
+        <v>11.88133430480957</v>
       </c>
       <c r="C80" t="n">
         <v>19.32999992370605</v>
@@ -2325,7 +2325,7 @@
         <v>43008</v>
       </c>
       <c r="B81" t="n">
-        <v>11.78913593292236</v>
+        <v>11.78913402557373</v>
       </c>
       <c r="C81" t="n">
         <v>19.18000030517578</v>
@@ -2354,7 +2354,7 @@
         <v>43039</v>
       </c>
       <c r="B82" t="n">
-        <v>11.20916175842285</v>
+        <v>11.20916080474854</v>
       </c>
       <c r="C82" t="n">
         <v>18.11000061035156</v>
@@ -2383,7 +2383,7 @@
         <v>43069</v>
       </c>
       <c r="B83" t="n">
-        <v>10.66448497772217</v>
+        <v>10.6644868850708</v>
       </c>
       <c r="C83" t="n">
         <v>17.22999954223633</v>
@@ -2441,7 +2441,7 @@
         <v>43131</v>
       </c>
       <c r="B85" t="n">
-        <v>11.20354843139648</v>
+        <v>11.20354557037354</v>
       </c>
       <c r="C85" t="n">
         <v>17.97999954223633</v>
@@ -2499,7 +2499,7 @@
         <v>43190</v>
       </c>
       <c r="B87" t="n">
-        <v>9.384061813354492</v>
+        <v>9.384065628051758</v>
       </c>
       <c r="C87" t="n">
         <v>15.0600004196167</v>
@@ -2528,7 +2528,7 @@
         <v>43220</v>
       </c>
       <c r="B88" t="n">
-        <v>9.980692863464355</v>
+        <v>9.980691909790039</v>
       </c>
       <c r="C88" t="n">
         <v>15.81999969482422</v>
@@ -2557,7 +2557,7 @@
         <v>43251</v>
       </c>
       <c r="B89" t="n">
-        <v>10.5232572555542</v>
+        <v>10.52326011657715</v>
       </c>
       <c r="C89" t="n">
         <v>16.68000030517578</v>
@@ -2586,7 +2586,7 @@
         <v>43281</v>
       </c>
       <c r="B90" t="n">
-        <v>11.14784049987793</v>
+        <v>11.14784336090088</v>
       </c>
       <c r="C90" t="n">
         <v>17.67000007629395</v>
@@ -2615,7 +2615,7 @@
         <v>43312</v>
       </c>
       <c r="B91" t="n">
-        <v>11.34398937225342</v>
+        <v>11.34399127960205</v>
       </c>
       <c r="C91" t="n">
         <v>17.78000068664551</v>
@@ -2642,7 +2642,7 @@
         <v>43343</v>
       </c>
       <c r="B92" t="n">
-        <v>11.29294776916504</v>
+        <v>11.29294872283936</v>
       </c>
       <c r="C92" t="n">
         <v>17.70000076293945</v>
@@ -2669,7 +2669,7 @@
         <v>43373</v>
       </c>
       <c r="B93" t="n">
-        <v>11.31208515167236</v>
+        <v>11.31208610534668</v>
       </c>
       <c r="C93" t="n">
         <v>17.72999954223633</v>
@@ -2696,7 +2696,7 @@
         <v>43404</v>
       </c>
       <c r="B94" t="n">
-        <v>10.99266147613525</v>
+        <v>10.99266242980957</v>
       </c>
       <c r="C94" t="n">
         <v>17.02000045776367</v>
@@ -2723,7 +2723,7 @@
         <v>43434</v>
       </c>
       <c r="B95" t="n">
-        <v>11.02495574951172</v>
+        <v>11.0249547958374</v>
       </c>
       <c r="C95" t="n">
         <v>17.06999969482422</v>
@@ -2750,7 +2750,7 @@
         <v>43465</v>
       </c>
       <c r="B96" t="n">
-        <v>9.933438301086426</v>
+        <v>9.933439254760742</v>
       </c>
       <c r="C96" t="n">
         <v>15.38000011444092</v>
@@ -2777,7 +2777,7 @@
         <v>43496</v>
       </c>
       <c r="B97" t="n">
-        <v>11.82118129730225</v>
+        <v>11.8211784362793</v>
       </c>
       <c r="C97" t="n">
         <v>18.10000038146973</v>
@@ -2804,7 +2804,7 @@
         <v>43524</v>
       </c>
       <c r="B98" t="n">
-        <v>12.51346874237061</v>
+        <v>12.51347064971924</v>
       </c>
       <c r="C98" t="n">
         <v>19.15999984741211</v>
@@ -2833,7 +2833,7 @@
         <v>43555</v>
       </c>
       <c r="B99" t="n">
-        <v>13.06861209869385</v>
+        <v>13.0686092376709</v>
       </c>
       <c r="C99" t="n">
         <v>20.01000022888184</v>
@@ -2862,7 +2862,7 @@
         <v>43585</v>
       </c>
       <c r="B100" t="n">
-        <v>13.13955307006836</v>
+        <v>13.13955020904541</v>
       </c>
       <c r="C100" t="n">
         <v>19.8700008392334</v>
@@ -2920,7 +2920,7 @@
         <v>43646</v>
       </c>
       <c r="B102" t="n">
-        <v>13.80743980407715</v>
+        <v>13.8074369430542</v>
       </c>
       <c r="C102" t="n">
         <v>20.8799991607666</v>
@@ -2949,7 +2949,7 @@
         <v>43677</v>
       </c>
       <c r="B103" t="n">
-        <v>13.80066871643066</v>
+        <v>13.80066394805908</v>
       </c>
       <c r="C103" t="n">
         <v>20.6200008392334</v>
@@ -2978,7 +2978,7 @@
         <v>43708</v>
       </c>
       <c r="B104" t="n">
-        <v>13.56641864776611</v>
+        <v>13.5664176940918</v>
       </c>
       <c r="C104" t="n">
         <v>20.27000045776367</v>
@@ -3007,7 +3007,7 @@
         <v>43738</v>
       </c>
       <c r="B105" t="n">
-        <v>13.79397678375244</v>
+        <v>13.79397201538086</v>
       </c>
       <c r="C105" t="n">
         <v>20.61000061035156</v>
@@ -3036,7 +3036,7 @@
         <v>43769</v>
       </c>
       <c r="B106" t="n">
-        <v>13.5401496887207</v>
+        <v>13.54014873504639</v>
       </c>
       <c r="C106" t="n">
         <v>19.97999954223633</v>
@@ -3065,7 +3065,7 @@
         <v>43799</v>
       </c>
       <c r="B107" t="n">
-        <v>13.28940582275391</v>
+        <v>13.28940773010254</v>
       </c>
       <c r="C107" t="n">
         <v>19.61000061035156</v>
@@ -3094,7 +3094,7 @@
         <v>43830</v>
       </c>
       <c r="B108" t="n">
-        <v>14.34659862518311</v>
+        <v>14.34659767150879</v>
       </c>
       <c r="C108" t="n">
         <v>21.17000007629395</v>
@@ -3152,7 +3152,7 @@
         <v>43890</v>
       </c>
       <c r="B110" t="n">
-        <v>13.1446418762207</v>
+        <v>13.14464092254639</v>
       </c>
       <c r="C110" t="n">
         <v>19.17000007629395</v>
@@ -3181,7 +3181,7 @@
         <v>43921</v>
       </c>
       <c r="B111" t="n">
-        <v>9.544776916503906</v>
+        <v>9.544777870178223</v>
       </c>
       <c r="C111" t="n">
         <v>13.92000007629395</v>
@@ -3210,7 +3210,7 @@
         <v>43951</v>
       </c>
       <c r="B112" t="n">
-        <v>10.44303035736084</v>
+        <v>10.44302940368652</v>
       </c>
       <c r="C112" t="n">
         <v>15.22999954223633</v>
@@ -3239,7 +3239,7 @@
         <v>43982</v>
       </c>
       <c r="B113" t="n">
-        <v>11.024245262146</v>
+        <v>11.02424812316895</v>
       </c>
       <c r="C113" t="n">
         <v>15.80000019073486</v>
@@ -3264,7 +3264,7 @@
         <v>44012</v>
       </c>
       <c r="B114" t="n">
-        <v>10.58466815948486</v>
+        <v>10.58467102050781</v>
       </c>
       <c r="C114" t="n">
         <v>15.17000007629395</v>
@@ -3314,7 +3314,7 @@
         <v>44074</v>
       </c>
       <c r="B116" t="n">
-        <v>9.823136329650879</v>
+        <v>9.823135375976562</v>
       </c>
       <c r="C116" t="n">
         <v>13.81999969482422</v>
@@ -3339,7 +3339,7 @@
         <v>44104</v>
       </c>
       <c r="B117" t="n">
-        <v>8.764056205749512</v>
+        <v>8.764057159423828</v>
       </c>
       <c r="C117" t="n">
         <v>12.32999992370605</v>
@@ -3364,7 +3364,7 @@
         <v>44135</v>
       </c>
       <c r="B118" t="n">
-        <v>8.646989822387695</v>
+        <v>8.646986961364746</v>
       </c>
       <c r="C118" t="n">
         <v>11.89999961853027</v>
@@ -3389,7 +3389,7 @@
         <v>44165</v>
       </c>
       <c r="B119" t="n">
-        <v>10.44904613494873</v>
+        <v>10.44904804229736</v>
       </c>
       <c r="C119" t="n">
         <v>14.38000011444092</v>
@@ -3439,7 +3439,7 @@
         <v>44227</v>
       </c>
       <c r="B121" t="n">
-        <v>10.41756534576416</v>
+        <v>10.41756629943848</v>
       </c>
       <c r="C121" t="n">
         <v>14.07999992370605</v>
@@ -3464,7 +3464,7 @@
         <v>44255</v>
       </c>
       <c r="B122" t="n">
-        <v>10.87629508972168</v>
+        <v>10.87629318237305</v>
       </c>
       <c r="C122" t="n">
         <v>14.69999980926514</v>
@@ -3489,7 +3489,7 @@
         <v>44286</v>
       </c>
       <c r="B123" t="n">
-        <v>12.31906986236572</v>
+        <v>12.31906795501709</v>
       </c>
       <c r="C123" t="n">
         <v>16.64999961853027</v>
@@ -3514,7 +3514,7 @@
         <v>44316</v>
       </c>
       <c r="B124" t="n">
-        <v>12.81339263916016</v>
+        <v>12.81339454650879</v>
       </c>
       <c r="C124" t="n">
         <v>17.04999923706055</v>
@@ -3589,7 +3589,7 @@
         <v>44408</v>
       </c>
       <c r="B127" t="n">
-        <v>13.26142883300781</v>
+        <v>13.26143074035645</v>
       </c>
       <c r="C127" t="n">
         <v>17.3799991607666</v>
@@ -3614,7 +3614,7 @@
         <v>44439</v>
       </c>
       <c r="B128" t="n">
-        <v>12.41446495056152</v>
+        <v>12.41446685791016</v>
       </c>
       <c r="C128" t="n">
         <v>16.27000045776367</v>
@@ -3639,7 +3639,7 @@
         <v>44469</v>
       </c>
       <c r="B129" t="n">
-        <v>12.76546192169189</v>
+        <v>12.76545906066895</v>
       </c>
       <c r="C129" t="n">
         <v>16.72999954223633</v>
@@ -3689,7 +3689,7 @@
         <v>44530</v>
       </c>
       <c r="B131" t="n">
-        <v>11.98289203643799</v>
+        <v>11.98289012908936</v>
       </c>
       <c r="C131" t="n">
         <v>15.46000003814697</v>
@@ -3714,7 +3714,7 @@
         <v>44561</v>
       </c>
       <c r="B132" t="n">
-        <v>12.29292774200439</v>
+        <v>12.29292678833008</v>
       </c>
       <c r="C132" t="n">
         <v>15.85999965667725</v>
@@ -3739,7 +3739,7 @@
         <v>44592</v>
       </c>
       <c r="B133" t="n">
-        <v>13.66666030883789</v>
+        <v>13.66665935516357</v>
       </c>
       <c r="C133" t="n">
         <v>17.36000061035156</v>
@@ -3764,7 +3764,7 @@
         <v>44620</v>
       </c>
       <c r="B134" t="n">
-        <v>13.69815063476562</v>
+        <v>13.69814968109131</v>
       </c>
       <c r="C134" t="n">
         <v>17.39999961853027</v>
@@ -3822,7 +3822,7 @@
         <v>44681</v>
       </c>
       <c r="B136" t="n">
-        <v>14.50293159484863</v>
+        <v>14.50293064117432</v>
       </c>
       <c r="C136" t="n">
         <v>18.14999961853027</v>
@@ -3851,7 +3851,7 @@
         <v>44712</v>
       </c>
       <c r="B137" t="n">
-        <v>15.73348331451416</v>
+        <v>15.73348617553711</v>
       </c>
       <c r="C137" t="n">
         <v>19.69000053405762</v>
@@ -3880,7 +3880,7 @@
         <v>44742</v>
       </c>
       <c r="B138" t="n">
-        <v>13.39223957061768</v>
+        <v>13.39224147796631</v>
       </c>
       <c r="C138" t="n">
         <v>16.76000022888184</v>
@@ -3909,7 +3909,7 @@
         <v>44773</v>
       </c>
       <c r="B139" t="n">
-        <v>14.60006999969482</v>
+        <v>14.60007190704346</v>
       </c>
       <c r="C139" t="n">
         <v>17.98999977111816</v>
@@ -3938,7 +3938,7 @@
         <v>44804</v>
       </c>
       <c r="B140" t="n">
-        <v>14.86788749694824</v>
+        <v>14.86789035797119</v>
       </c>
       <c r="C140" t="n">
         <v>18.31999969482422</v>
@@ -3967,7 +3967,7 @@
         <v>44834</v>
       </c>
       <c r="B141" t="n">
-        <v>13.50445747375488</v>
+        <v>13.50445938110352</v>
       </c>
       <c r="C141" t="n">
         <v>16.63999938964844</v>
@@ -3996,7 +3996,7 @@
         <v>44865</v>
       </c>
       <c r="B142" t="n">
-        <v>14.9363899230957</v>
+        <v>14.93638801574707</v>
       </c>
       <c r="C142" t="n">
         <v>18.1200008392334</v>
@@ -4025,7 +4025,7 @@
         <v>44895</v>
       </c>
       <c r="B143" t="n">
-        <v>15.76069259643555</v>
+        <v>15.76069641113281</v>
       </c>
       <c r="C143" t="n">
         <v>19.1200008392334</v>
@@ -4054,7 +4054,7 @@
         <v>44926</v>
       </c>
       <c r="B144" t="n">
-        <v>14.90342140197754</v>
+        <v>14.90341663360596</v>
       </c>
       <c r="C144" t="n">
         <v>18.07999992370605</v>
@@ -4083,7 +4083,7 @@
         <v>44957</v>
       </c>
       <c r="B145" t="n">
-        <v>15.31289768218994</v>
+        <v>15.31289577484131</v>
       </c>
       <c r="C145" t="n">
         <v>18.29999923706055</v>
@@ -4112,7 +4112,7 @@
         <v>44985</v>
       </c>
       <c r="B146" t="n">
-        <v>14.27530384063721</v>
+        <v>14.27530193328857</v>
       </c>
       <c r="C146" t="n">
         <v>17.05999946594238</v>
@@ -4170,7 +4170,7 @@
         <v>45046</v>
       </c>
       <c r="B148" t="n">
-        <v>14.58899021148682</v>
+        <v>14.58898735046387</v>
       </c>
       <c r="C148" t="n">
         <v>17.14999961853027</v>
@@ -4228,7 +4228,7 @@
         <v>45107</v>
       </c>
       <c r="B150" t="n">
-        <v>14.64853477478027</v>
+        <v>14.64853382110596</v>
       </c>
       <c r="C150" t="n">
         <v>17.21999931335449</v>
@@ -4257,7 +4257,7 @@
         <v>45138</v>
       </c>
       <c r="B151" t="n">
-        <v>15.30875682830811</v>
+        <v>15.30875492095947</v>
       </c>
       <c r="C151" t="n">
         <v>17.70999908447266</v>
@@ -4286,7 +4286,7 @@
         <v>45169</v>
       </c>
       <c r="B152" t="n">
-        <v>14.88519191741943</v>
+        <v>14.88519096374512</v>
       </c>
       <c r="C152" t="n">
         <v>17.21999931335449</v>
@@ -4344,7 +4344,7 @@
         <v>45230</v>
       </c>
       <c r="B154" t="n">
-        <v>14.24983978271484</v>
+        <v>14.24984073638916</v>
       </c>
       <c r="C154" t="n">
         <v>16.20000076293945</v>
@@ -4373,7 +4373,7 @@
         <v>45260</v>
       </c>
       <c r="B155" t="n">
-        <v>15.45491695404053</v>
+        <v>15.45491600036621</v>
       </c>
       <c r="C155" t="n">
         <v>17.56999969482422</v>
@@ -4402,7 +4402,7 @@
         <v>45291</v>
       </c>
       <c r="B156" t="n">
-        <v>15.5164909362793</v>
+        <v>15.51648998260498</v>
       </c>
       <c r="C156" t="n">
         <v>17.63999938964844</v>
@@ -4431,7 +4431,7 @@
         <v>45322</v>
       </c>
       <c r="B157" t="n">
-        <v>15.12966346740723</v>
+        <v>15.12966632843018</v>
       </c>
       <c r="C157" t="n">
         <v>16.92000007629395</v>
@@ -4489,7 +4489,7 @@
         <v>45382</v>
       </c>
       <c r="B159" t="n">
-        <v>16.39941024780273</v>
+        <v>16.39941215515137</v>
       </c>
       <c r="C159" t="n">
         <v>18.34000015258789</v>
@@ -4576,7 +4576,7 @@
         <v>45473</v>
       </c>
       <c r="B162" t="n">
-        <v>18.04574394226074</v>
+        <v>18.04574012756348</v>
       </c>
       <c r="C162" t="n">
         <v>19.8700008392334</v>
@@ -4634,7 +4634,7 @@
         <v>45535</v>
       </c>
       <c r="B164" t="n">
-        <v>19.85290908813477</v>
+        <v>19.85290718078613</v>
       </c>
       <c r="C164" t="n">
         <v>21.56999969482422</v>
@@ -4663,7 +4663,7 @@
         <v>45565</v>
       </c>
       <c r="B165" t="n">
-        <v>20.33151245117188</v>
+        <v>20.33151626586914</v>
       </c>
       <c r="C165" t="n">
         <v>22.09000015258789</v>
@@ -4692,7 +4692,7 @@
         <v>45596</v>
       </c>
       <c r="B166" t="n">
-        <v>22.823486328125</v>
+        <v>22.82348823547363</v>
       </c>
       <c r="C166" t="n">
         <v>24.51000022888184</v>
@@ -4721,7 +4721,7 @@
         <v>45626</v>
       </c>
       <c r="B167" t="n">
-        <v>26.32476806640625</v>
+        <v>26.32476425170898</v>
       </c>
       <c r="C167" t="n">
         <v>28.27000045776367</v>
@@ -4750,7 +4750,7 @@
         <v>45657</v>
       </c>
       <c r="B168" t="n">
-        <v>25.51462936401367</v>
+        <v>25.51462554931641</v>
       </c>
       <c r="C168" t="n">
         <v>27.39999961853027</v>
@@ -4779,7 +4779,7 @@
         <v>45688</v>
       </c>
       <c r="B169" t="n">
-        <v>25.5891227722168</v>
+        <v>25.58912467956543</v>
       </c>
       <c r="C169" t="n">
         <v>27.47999954223633</v>
@@ -4808,7 +4808,7 @@
         <v>45716</v>
       </c>
       <c r="B170" t="n">
-        <v>25.50254821777344</v>
+        <v>25.5025463104248</v>
       </c>
       <c r="C170" t="n">
         <v>27.10000038146973</v>
@@ -4953,7 +4953,7 @@
         <v>45869</v>
       </c>
       <c r="B175" t="n">
-        <v>26.97557258605957</v>
+        <v>26.9755744934082</v>
       </c>
       <c r="C175" t="n">
         <v>28.05999946594238</v>
@@ -4982,7 +4982,7 @@
         <v>45900</v>
       </c>
       <c r="B176" t="n">
-        <v>25.93731307983398</v>
+        <v>25.93731117248535</v>
       </c>
       <c r="C176" t="n">
         <v>26.97999954223633</v>
@@ -5011,7 +5011,7 @@
         <v>45930</v>
       </c>
       <c r="B177" t="n">
-        <v>27.21591186523438</v>
+        <v>27.21591377258301</v>
       </c>
       <c r="C177" t="n">
         <v>28.30999946594238</v>
@@ -5040,7 +5040,7 @@
         <v>45961</v>
       </c>
       <c r="B178" t="n">
-        <v>25.17784309387207</v>
+        <v>25.17784690856934</v>
       </c>
       <c r="C178" t="n">
         <v>26.19000053405762</v>
@@ -5069,7 +5069,7 @@
         <v>45991</v>
       </c>
       <c r="B179" t="n">
-        <v>26.56132888793945</v>
+        <v>26.56132698059082</v>
       </c>
       <c r="C179" t="n">
         <v>27.31999969482422</v>
@@ -5098,7 +5098,7 @@
         <v>46022</v>
       </c>
       <c r="B180" t="n">
-        <v>26.72660827636719</v>
+        <v>26.72660636901855</v>
       </c>
       <c r="C180" t="n">
         <v>27.48999977111816</v>
@@ -5127,7 +5127,7 @@
         <v>46053</v>
       </c>
       <c r="B181" t="n">
-        <v>29.6432991027832</v>
+        <v>29.64329719543457</v>
       </c>
       <c r="C181" t="n">
         <v>30.48999977111816</v>
